--- a/data/trans_camb/IP21-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP21-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-3.994832656133281</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.539637257815898</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.7897207959835888</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.966732074547493</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-2.439472855175998</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-3.752834659275624</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-7.044530790664489</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.628556708752965</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.355969770426494</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.287727778041973</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-4.46887497387309</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-5.631732603147153</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-1.21376199015442</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-1.462998627879326</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.680734978602244</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>-0.3081140434550082</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>-0.4703084730729072</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-1.800299204384532</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.6495954248215107</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.7381855128522036</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.2130340879991807</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.8003019105657138</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4921596518853496</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.7571282441505636</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.8603822187502147</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.9392370221629561</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.6408215567616488</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7110304351838816</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.9231518029716047</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>-0.2315374927274556</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-0.1430238431680521</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.8035200255415965</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.7980995099887294</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.09018615773857536</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.4013573174013097</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>0.5632542473830854</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.399490785565921</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.481225431265074</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.644922515540117</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.458526334334171</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-3.056182923883575</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-2.28045183951717</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.730867439453084</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.304347129307324</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.502432077927786</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-3.468783408478149</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-4.941832332252729</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>3.303419927891108</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>-0.5083146440440379</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-0.9106552824849764</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-0.8326099345368596</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.6615383463015869</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-1.362160620932841</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.1893151413349588</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.8064918095369257</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.6540255963767445</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.6847797331834531</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.351372014529587</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.7362617495872088</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.5658171601191339</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.8777594099275016</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8933330638835257</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6459973702382111</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.9066035469666176</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>2.061576419128415</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.7866924362674195</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-0.06460777620159829</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-0.02785441141340278</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2724839408033307</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>-0.3331012715919078</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-1.106727464223028</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.772282703261481</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.07538372135047766</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.087238881654037</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.5925188452940967</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-2.434539705506066</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-4.932916262917654</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.115911810467646</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.38239265450115</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.483321536633748</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-3.444210624289896</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-4.870624830535111</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>2.870213247218464</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-0.004592074445437714</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.975188311082131</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.9594031167099726</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.917181990870811</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-0.4274429880239463</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.2326858875524853</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.5828635162746862</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.01851058293907384</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.5125245575618157</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.1340810143245276</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.5509116810716268</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.7249256848405204</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.8648622463735595</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.6249184705814392</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.8493080732681315</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.5750706872555597</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.7889859896515832</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>1.10970765637787</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.1332900962987035</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>2.305971302640206</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.820177811262637</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.5651465497613883</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-0.08516770207145162</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.8169575171176804</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.07364773344351282</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2.456321863158237</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.392527555469239</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.6269421221752545</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.7394437989043646</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-4.767011468736201</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-3.830199345916832</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.713003260246169</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-5.556151526523508</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-2.006091289477078</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-3.105984084848784</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>2.1183642056175</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.705542734914897</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>7.54975254469404</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.9061544552178888</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>3.650250372755993</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1.541790482306507</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.2956568587172608</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.02665310871779225</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>1.067152021003344</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.6049852901651733</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.2455537825971561</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.2896171997647669</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,22 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.8989760264575531</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.747265683341244</v>
+      </c>
       <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.5436736481715974</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.7979563036301294</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1208,20 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>4.568361057012717</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>6.401592090162342</v>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>2.826806402860318</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.248005811766091</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1234,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.635326112513789</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-2.787297248324421</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-1.079162604428965</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-2.678033702562888</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.364504365837686</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-2.729925831578502</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1260,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-3.455526716599191</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-4.32802888490997</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-2.69930658315445</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-4.147035769458967</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-2.495590178136112</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-3.803461027784993</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1286,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-0.06569980693870552</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>-1.362236424610169</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.5421859306289848</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-1.206289235151055</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.1506046334058697</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-1.664312219665953</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1312,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.3685159624080323</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>-0.6281092927725589</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.2607368871623526</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.6470407410860941</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.3179564904994803</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.6361266834054439</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1338,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.6141938728834022</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.7957080112234856</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.5253999734525122</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.8095413909795096</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.509684520254746</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.7601447262280039</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1364,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.005007793213273248</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-0.3185595492070071</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.194277572463065</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>-0.3512544341369468</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.04229638196790438</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>-0.4331833995886679</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1392,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
